--- a/02_加值成品/九上/九上3-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上3-4_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上3-4 能源與科技　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三上學期 九上3-4 能源與科技　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>煤、石油、天然氣屬於？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>化石燃料</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>二氧化碳</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>太陽能</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>汽電共生</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>不可再生</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>太陽能、風力屬於？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>再生能源</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>汽電共生</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>省油減碳</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>太陽能</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>可再生</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>化石燃料燃燒會排放？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>化石燃料</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>進口化石燃料</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>二氧化碳</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>日照</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>排碳</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>氫能發電的裝置是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>化石燃料</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>燃料電池</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>進口化石燃料</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>二氧化碳</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>新興</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>同時供熱與電的技術是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>化石燃料</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>二氧化碳</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>汽電共生</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>熱電</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>臺灣能源主要靠？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>進口化石燃料</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>能源利用效率</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>燃料電池</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>依賴進口</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>油電混合車的優點？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>二氧化碳</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>進口化石燃料</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>較乾淨可再生</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>省油減碳</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>混合動力</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>可不斷補充的能源稱？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>化石燃料</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>再生能源</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>燃料電池</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>太陽能</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>永續</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>風力發電屬再生還不可再生能源？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>再生能源</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>二氧化碳</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>日照</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>太陽能</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>可再生</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>燃燒化石燃料主要排放哪種溫室氣體？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>二氧化碳</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>太陽能</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>燃料電池</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>日照</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>排碳</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上3-4 能源與科技　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三上學期 九上3-4 能源與科技　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>再生能源的優點？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>日照</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>較乾淨可再生</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>汽電共生</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>環保</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>化石燃料的缺點？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>排碳且會枯竭</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>燃料電池</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>太陽能</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>日照</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>污染有限</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>燃料電池把什麼能轉電能？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>低速用電並回收煞車能量</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>可再生且污染較低</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>低速用電、回收煞車能量</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>化學能(氫氧)</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>轉換</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>太陽能飛機動力來自？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>二氧化碳</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>燃料電池</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>太陽能</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>再生能源</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>再生</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>地熱能屬於再生能源嗎？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>省油減碳</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>日照</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>汽電共生</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>可再生</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>臺灣推動離岸風電屬？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>再生能源</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>汽電共生</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>日照</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>風力</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>核能是再生能源嗎？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>燃料電池</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>不是</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>省油減碳</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>二氧化碳</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>核燃料有限</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>汽電共生提高了什麼？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>太陽能</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>能源利用效率</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>汽電共生</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>效率</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>太陽能發電依賴什麼條件？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>日照</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>排碳且會枯竭</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>燃料電池</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>汽電共生</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>天候</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>地熱與潮汐能屬於？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>進口化石燃料</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>二氧化碳</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>太陽能</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>再生能源</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>可再生</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上3-4 能源與科技　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三上學期 九上3-4 能源與科技　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何說再生能源並非零污染？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>可再生且污染較低</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>節電、大眾運輸、減少浪費</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>設備製造與建置仍有環境成本</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>乾淨但受天候日照限制</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>客觀</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>分析臺灣為何要發展再生能源？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>廢熱再利用發電或供暖</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>再生與新興能源</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>設備製造與建置仍有環境成本</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>減少進口依賴與排碳、提升能源安全</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>策略</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>燃料電池與一般電池差別？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>燃料電池持續供燃料發電、不需充電</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>減少進口依賴與排碳、提升能源安全</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>廢熱再利用發電或供暖</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>可再生且污染較低</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>原理</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>油電混合車如何省油？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>低速用電、回收煞車能量</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>低速用電並回收煞車能量</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>乾淨但受天候日照限制</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>化學能(氫氧)</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>機制</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>評估太陽能的優缺點？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>低速用電並回收煞車能量</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>燃料電池持續供燃料發電、不需充電</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>再生與新興能源</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>乾淨但受天候日照限制</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>評估</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>汽電共生為何提升整體效率？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>乾淨但受天候日照限制</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>化學能(氫氧)</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>廢熱再利用發電或供暖</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>低速用電、回收煞車能量</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>效率</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>個人如何為節能減碳出力？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>可再生且污染較低</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>設備製造與建置仍有環境成本</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>燃料電池持續供燃料發電、不需充電</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>節電、大眾運輸、減少浪費</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>行動</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>化石燃料枯竭的隱憂促使發展？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>設備製造與建置仍有環境成本</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>再生與新興能源</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>乾淨但受天候日照限制</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>低速用電、回收煞車能量</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>趨勢</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何再生能源被視為較永續？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>廢熱再利用發電或供暖</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>乾淨但受天候日照限制</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>可再生且污染較低</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>化學能(氫氧)</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>永續</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>油電混合車省油的關鍵？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>節電、大眾運輸、減少浪費</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>減少進口依賴與排碳、提升能源安全</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>設備製造與建置仍有環境成本</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>低速用電並回收煞車能量</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>機制</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九上/九上3-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上3-4_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>不可再生</t>
+          <t>不可再生：這三種都是古代生物遺骸經長久時間變成的燃料,用完不會再生</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>可再生</t>
+          <t>可再生：陽光和風會不斷出現,取用之後還會持續補充,所以叫再生能源</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>排碳</t>
+          <t>排碳：燃燒煤、石油、天然氣時,會產生大量二氧化碳排到空氣中</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>新興</t>
+          <t>新興：燃料電池利用氫和氧反應,直接把化學能轉換成電能</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>熱電</t>
+          <t>熱電：發電過程中產生的廢熱拿來供暖或加熱,同時得到電和熱兩種用途</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>依賴進口</t>
+          <t>依賴進口：臺灣自己缺乏石油煤礦,大部分能源都要從國外買進來</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>混合動力</t>
+          <t>混合動力：同時使用汽油引擎和電動馬達,能減少耗油量和排放的廢氣</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>永續</t>
+          <t>永續：像陽光、風、水這些用了之後還會自然補充回來的能源</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>可再生</t>
+          <t>可再生：風是大自然中會不斷產生、用不完的資源,所以風力發電屬於再生能源</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>排碳</t>
+          <t>排碳：石油、煤炭等化石燃料燃燒時會產生大量二氧化碳,是造成溫室效應的主要氣體之一</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>環保</t>
+          <t>環保：使用時幾乎不排放污染物,而且來源可以不斷補充使用</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>污染有限</t>
+          <t>污染有限：燃燒會排放大量二氧化碳造成污染,而且蘊藏量有限總有用完的一天</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>轉換</t>
+          <t>轉換：燃料電池讓氫氣和氧氣進行化學反應,直接把化學能轉換成電能</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>再生</t>
+          <t>再生：機翼上裝設太陽能板吸收陽光,轉換成電力驅動飛機的馬達</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>可再生</t>
+          <t>可再生：地球內部的熱能會持續產生,不會因為使用而耗盡,屬於再生能源</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>風力</t>
+          <t>風力：在海上架設風力發電機利用風力發電,是一種再生能源</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>核燃料有限</t>
+          <t>核燃料有限：核能發電需要用到鈾等核燃料,這些礦產蘊藏量有限,並非再生能源</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>效率</t>
+          <t>效率：把原本會浪費的廢熱拿來利用,讓整體的能源使用效率提高</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>天候</t>
+          <t>天候：太陽能板需要有陽光照射才能發電,所以發電量會受天氣、日夜、季節等日照條件影響</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>可再生</t>
+          <t>可再生：地球內部熱能與潮汐現象會持續存在、不斷提供能量,所以地熱能和潮汐能都屬於再生能源</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>客觀</t>
+          <t>客觀：太陽能板風機在製造、運輸、建置過程中,還是會消耗能源產生污染</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>策略</t>
+          <t>策略：發展再生能源能降低對進口化石燃料的依賴,減少碳排放,也讓能源供應更穩定安全</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>原理</t>
+          <t>原理：一般電池電用完要充電,燃料電池只要不斷補充氫氣燃料就能持續發電</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>機制</t>
+          <t>機制：低速時改用電動馬達省油,煞車時還能把原本浪費的能量回收儲存起來</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>評估</t>
+          <t>評估：太陽能發電乾淨不排污染,但下雨天或晚上沒有陽光就無法發電,很受天氣影響</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>效率</t>
+          <t>效率：發電過程本來會浪費的廢熱,拿來供暖或再次發電,讓能源沒有白白浪費</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>行動</t>
+          <t>行動：隨手關燈省電、多搭乘大眾運輸工具、減少不必要的浪費,都能幫忙節能減碳</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>趨勢</t>
+          <t>趨勢：因為擔心化石燃料有一天會用完,各國才積極開發太陽能風力等再生能源</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>永續</t>
+          <t>永續：再生能源來自陽光、風、水等會不斷補充的資源,用了不會枯竭,而且發電過程通常污染較少,所以被認為比較永續</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>機制</t>
+          <t>機制：油電混合車在低速時改用電動馬達行駛,並在煞車時把原本浪費掉的動能回收轉存成電能,因此比純燃油車省油</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九上/九上3-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上3-4_三種難度測驗卷.xlsx
@@ -568,17 +568,17 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>二氧化碳</t>
+          <t>排碳且會枯竭</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
+          <t>能源利用效率</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
           <t>太陽能</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>汽電共生</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -773,12 +773,12 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>燃料電池</t>
+          <t>二氧化碳</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>不是</t>
+          <t>省油減碳</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1199,14 +1199,14 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
+          <t>太陽能</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
           <t>省油減碳</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>日照</t>
-        </is>
-      </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
           <t>是</t>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>汽電共生</t>
+          <t>燃料電池</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1279,22 +1279,22 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
+          <t>再生能源</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>進口化石燃料</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
           <t>燃料電池</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>不是</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>省油減碳</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>二氧化碳</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
